--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dponti/Documents/GitHub/def/Codelist Excel Files and Conversion Templates to XML/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2951FA94-EB27-4B45-A512-E35058B51E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327A5682-C449-DD43-8FB4-47B7F498E61A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10020" yWindow="2560" windowWidth="35840" windowHeight="20700" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10020" yWindow="2560" windowWidth="35840" windowHeight="20700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DictionaryName" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2472" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2473" uniqueCount="968">
   <si>
     <t>Start</t>
   </si>
@@ -8091,6 +8091,9 @@
       <c r="E199" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="F199" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="200" spans="1:6" ht="34">
       <c r="A200" s="2" t="str">

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J218"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -7789,6 +7789,104 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219">
+        <f>IF(ISNA(VLOOKUP(B219,AssociatedElements!B$2:B850,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>apparent_resistivity_min</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Minimum Apparent Resistivity</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>The minimum apparent resistivity value among the readings taken during an in-situ electrical resistivity test at a station, used together with the maximum apparent resistivity to characterize the resistivity range for a corrosivity classification (eg. Palmer, 1974).</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>electrical resistivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <f>IF(ISNA(VLOOKUP(B220,AssociatedElements!B$2:B850,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>apparent_resistivity_max</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Maximum Apparent Resistivity</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>The maximum apparent resistivity value among the readings taken during an in-situ electrical resistivity test at a station, used together with the minimum apparent resistivity to characterize the resistivity range for a corrosivity classification (eg. Palmer, 1974).</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>electrical resistivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <f>IF(ISNA(VLOOKUP(B221,AssociatedElements!B$2:B850,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>corrosivity_classification_palmer</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Corrosivity Classification (Palmer, 1974)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>A qualitative soil corrosivity rating for buried metal, assigned from the apparent resistivity range measured by an in-situ electrical resistivity test according to the correlation published by Palmer (1974): 0-10 ohm.m Very Severe, 11-20 Severe, 21-50 Moderate, 51-100 Mild, 101+ Very Mild.</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>J.D. Palmer</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Palmer, J.D. (1974). Soil Resistivity - Measurement and Analysis. Material Performance, Vol. 13.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7804,7 +7902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D349"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15073,6 +15171,69 @@
       <c r="D346" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabCBRTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <f>IF(ISNA(VLOOKUP(B347,Definitions!B$2:B$1604,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>apparent_resistivity_min</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:InsituResistivityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <f>IF(ISNA(VLOOKUP(B348,Definitions!B$2:B$1604,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>apparent_resistivity_max</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:InsituResistivityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <f>IF(ISNA(VLOOKUP(B349,Definitions!B$2:B$1604,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>corrosivity_classification_palmer</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:InsituResistivityTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A1:J223"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -7887,6 +7887,60 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>thermal_conductivity</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Thermal Conductivity</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>A material's ability to conduct heat, determined for soil or soft rock by the thermal needle probe method (ASTM D5334, IEEE Std 442).</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>thermal conductivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>thermal_resistivity</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Thermal Resistivity</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>The reciprocal of thermal conductivity - a material's opposition to heat flow per unit length - determined for soil or soft rock by the thermal needle probe method (ASTM D5334, IEEE Std 442).</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>thermal resistivity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -7902,7 +7956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D351"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15234,6 +15288,40 @@
       <c r="D349" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:InsituResistivityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>thermal_conductivity</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabThermalConductivityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>thermal_resistivity</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabThermalConductivityTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J223"/>
+  <dimension ref="A1:J228"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Chloride content by lab testing (corrosivity series)</t>
+          <t>Chloride content of soil or groundwater by laboratory testing (corrosivity series). USE THIS ENTRY WHEN THE SOURCE DOES NOT STATE THE EXTRACTION BASIS - the case for the Jazera project record (GBL-24136), which reports a chloride content as a percentage without saying whether it is water- or acid-soluble. Where the basis IS known, prefer chloride_water_soluble or chloride_acid_soluble instead.</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>Sulfate content by lab testing (corrosivity series)</t>
+          <t>Sulfate content of soil or groundwater by laboratory testing (corrosivity series). USE THIS ENTRY WHEN THE SOURCE DOES NOT STATE THE EXTRACTION BASIS - common in practice, and the case for the Jazera project record (GBL-24136), which reports a sulfate content in ppm without saying whether it is water- or acid-soluble. Where the basis IS known, prefer the specific entry instead: sulfate_water_soluble or sulfate_acid_soluble. The distinction is not cosmetic - the two can differ by an order of magnitude on the same material, and BS 8500 / BRE Special Digest 1 derive their ACEC class from a particular one of them.</t>
         </is>
       </c>
       <c r="E156" s="15" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="D213" s="38" t="inlineStr">
         <is>
-          <t>Magnesium content by lab testing (corrosivity series). Completes the chemistry set the ground-aggressivity classifications are derived from: EN 206 grades chemical attack partly on magnesium ion content, and BS 8500 derives its ACEC class from sulfate AND magnesium together via BRE Special Digest 1, so an exposureClassification could be stated without the measurement that justifies it. Added at R10 from the Jazera project record (GBL-24136), which reports 571-954 ppm alongside its sulfate, chloride and pH results.</t>
+          <t>Magnesium content by lab testing (corrosivity series). Completes the chemistry set the ground-aggressivity classifications are derived from: EN 206 grades chemical attack partly on magnesium ion content, and BS 8500 derives its ACEC class from sulfate AND magnesium together via BRE Special Digest 1, so an exposureClassification could be stated without the measurement that justifies it. Added at R10 from the Jazera project record (GBL-24136), which reports 571-954 ppm alongside its sulfate, chloride and pH results. USE THIS ENTRY WHEN THE SOURCE DOES NOT STATE THE EXTRACTION BASIS, as that record does not; where it is known to be the water-soluble determination of BS 1377-3 Clause 10, prefer magnesium_water_soluble instead.</t>
         </is>
       </c>
       <c r="E213" s="38" t="inlineStr">
@@ -7938,6 +7938,141 @@
       <c r="F223" t="inlineStr">
         <is>
           <t>thermal resistivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>sulfate_water_soluble</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Sulfate Content, Water-Soluble</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Water-soluble sulfate content of soil or groundwater - the fraction released by a water extract, conventionally the 2:1 water:soil extract of BS 1377-3 Clause 7, and the quantity determined by ASTM C1580 and AASHTO T 290. Use in preference to the generic sulfate_content whenever the source states that the determination was water-soluble. Distinguish from sulfate_acid_soluble: the two can differ by an order of magnitude on the same material, and BS 8500 / BRE Special Digest 1 ACEC classification depends on which was measured.</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>sulfate_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Sulfate Content, Acid-Soluble</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Acid-soluble sulfate content of soil - the fraction released by acid digestion, per BS 1377-3 Clause 7, and generally the larger of the two determinations because it mobilises sparingly-soluble sulfate minerals such as gypsum that a water extract leaves behind. Use in preference to the generic sulfate_content whenever the source states that the determination was acid-soluble. Distinct again from total sulfur and from the sulfide determinations of the same clause, which are different analytes rather than different extractions.</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>chloride_water_soluble</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Chloride Content, Water-Soluble</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Water-soluble chloride content of soil or groundwater - the fraction released by a water extract, per BS 1377-3 Clause 9 and AASHTO T 291. Use in preference to the generic chloride_content whenever the source states that the determination was water-soluble.</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>chloride_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Chloride Content, Acid-Soluble</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Acid-soluble chloride content of soil - the fraction released by acid digestion, per BS 1377-3 Clause 9. Use in preference to the generic chloride_content whenever the source states that the determination was acid-soluble.</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>magnesium_water_soluble</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Magnesium Content, Water-Soluble</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Water-soluble magnesium content of soil or groundwater, per BS 1377-3 Clause 10 - which specifies the water-soluble determination only, so for magnesium this is the basis a BS 1377-3 result will normally be on even when the report does not say so. Use in preference to the generic magnesium_content whenever the source confirms it. Magnesium matters because BS 8500 derives its ACEC class from sulfate and magnesium together via BRE Special Digest 1, and EN 206 grades chemical attack partly on magnesium ion content.</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
         </is>
       </c>
     </row>
@@ -7956,7 +8091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D351"/>
+  <dimension ref="A1:D356"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15322,6 +15457,91 @@
       <c r="D351" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabThermalConductivityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>sulfate_water_soluble</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>sulfate_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>chloride_water_soluble</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>chloride_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>magnesium_water_soluble</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J228"/>
+  <dimension ref="A1:J234"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="D117" s="28" t="inlineStr">
         <is>
-          <t>A meassure of how acidic or basic a soil or water is.</t>
+          <t>The negative base-10 logarithm of hydrogen ion activity in a soil-water suspension or in a water sample - the measure of how acidic or alkaline the material is, on a scale where 7 is neutral, lower values are acidic and higher values alkaline. Dimensionless by definition, so a Property carrying it states no uom. Determined electrometrically with a pH meter: BS 1377-3 Clause 12; ASTM G51 and AASHTO T 289 where the purpose is corrosion assessment; ASTM D4972 for agricultural, environmental and natural-resource purposes, whose own scope excludes corrosion testing. In a ground-aggressivity assessment pH is read together with resistivity, sulfate and chloride rather than on its own.</t>
         </is>
       </c>
       <c r="E117" s="35" t="inlineStr">
@@ -8071,6 +8071,168 @@
         </is>
       </c>
       <c r="F228" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>total_organic_carbon</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Total Organic Carbon</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Total organic carbon (TOC) content of soil, per BS 1377-3 Clause 5 - the carbon held in organic compounds, determined after removing carbonate carbon. Distinct from total_carbon and easily_oxidized_carbon, which are the AASHTO T 194 wet-combustion determinations bound to OrganicMatterByWetCombustionTest, and distinct again from LOI (loss on ignition, Clause 6) and total_organic_matter, which measure organic MATTER rather than the carbon within it.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>carbonate_content</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Carbonate Content</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Carbonate content of soil, per BS 1377-3 Clause 8, usually expressed as equivalent calcium carbonate. Relevant both to ground aggressivity - carbonate buffers acidity and moderates the pH a corrosion assessment reads - and to the identification of calcareous and cemented soils. The Jazera site's sabkha and calcareous sands are exactly the materials for which this is normally reported, though this determination is not in the project record.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>total_sulfur</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Total Sulfur</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Total sulfur content of soil, per BS 1377-3 Clause 7 - all sulfur present, in every oxidation state, not only that recoverable as sulfate. The upper bound on sulfate that could develop if reduced sulfur compounds oxidise, which is why it is reported for pyritic and sabkha ground. A DIFFERENT ANALYTE from sulfate_content and its water- and acid-soluble variants, not another extraction of the same one.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>total_sulfide</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Total Sulfide</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Total sulfide content of soil, also called total reduced sulfur, per BS 1377-3 Clause 7 - sulfur held in reduced form, which on exposure to air can oxidise to sulfate and acidify the ground. Reported where pyrite or organic-rich anaerobic deposits are suspected. Distinct from sulfide_acid_soluble, which recovers only the monosulfide fraction.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>sulfide_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Sulfide Content, Acid-Soluble</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Acid-soluble sulfide content of soil - the monosulfide fraction released by acid digestion, per BS 1377-3 Clause 7. A subset of total_sulfide: it does not recover disulfides such as pyrite, so the two differ substantially in pyritic ground and should not be used interchangeably.</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>amount of substance per amount of substance</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>total_dissolved_solids</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Total Dissolved Solids</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Total dissolved solids (TDS) of groundwater, per BS 1377-3 Clause 11 - the mass of dissolved material remaining after evaporation of a filtered sample. A summary measure of groundwater salinity, read alongside the individual ion determinations (sulfate, chloride, magnesium) rather than in place of them.</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
         <is>
           <t>amount of substance per amount of substance</t>
         </is>
@@ -8091,7 +8253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D356"/>
+  <dimension ref="A1:D366"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15540,6 +15702,176 @@
         </is>
       </c>
       <c r="D356" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>total_organic_carbon</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>carbonate_content</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>total_sulfur</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>total_sulfide</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>sulfide_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>total_dissolved_solids</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>LOI</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>resistivity</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>redox_potential</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>total_organic_matter</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
         </is>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1823,7 +1823,7 @@
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="G24" s="11" t="n"/>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="F213" s="38" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8207,7 +8207,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -8234,7 +8234,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -3824,7 +3824,7 @@
       </c>
       <c r="F89" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J89" s="38" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="F182" s="38" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="F183" s="38" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="F184" s="38" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="F185" s="38" t="inlineStr">
         <is>
-          <t>amount of substance per amount of substance</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1260,12 +1260,17 @@
       </c>
       <c r="D7" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The ratio, (by weight) of particles whose greatest dimension (length) is 1.8 times their mean dimension to the total weight of the sample.</t>
+          <t xml:space="preserve"> The ratio, (by mass) of particles whose greatest dimension (length) is 1.8 times their mean dimension to the total mass of the sample.</t>
         </is>
       </c>
       <c r="E7" s="38" t="inlineStr">
         <is>
           <t>double</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1291,7 @@
       </c>
       <c r="D8" s="38" t="inlineStr">
         <is>
-          <t>Percentage (by weight) of aggregate particles whose least dimension is less than 0.6 times their mean size, to the total sample weight.</t>
+          <t>Percentage (by mass) of aggregate particles whose least dimension is less than 0.6 times their mean size, to the total sample mass.</t>
         </is>
       </c>
       <c r="E8" s="38" t="inlineStr">
@@ -1296,7 +1301,7 @@
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J8" s="38" t="inlineStr">
@@ -1322,7 +1327,7 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The resistance to impact of aggregates and is measured as the fraction  of aggregates passing to the total weight of the sample.</t>
+          <t xml:space="preserve"> The resistance to impact of aggregates and is measured as the fraction  of aggregates passing to the total mass of the sample.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1332,7 +1337,7 @@
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J9" s="38" t="inlineStr">
@@ -1358,7 +1363,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The actual measured loss (difference between the original weight and the final weight of the test sample), expressed as a percentage of the original weight of the test sample.</t>
+          <t xml:space="preserve"> The actual measured loss (difference between the original mass and the final mass of the test sample), expressed as a percentage of the original mass of the test sample.</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -1368,7 +1373,7 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J10" s="38" t="inlineStr">
@@ -1421,7 +1426,7 @@
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The actual measured loss (difference between the original weight and the final weight of the test sample), expressed as an integer ratio of the original weight of the test sample. </t>
+          <t xml:space="preserve"> The actual measured loss (difference between the original mass and the final mass of the test sample), expressed as an integer ratio of the original mass of the test sample. </t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1429,7 +1434,11 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>mass per mass</t>
+        </is>
+      </c>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
     </row>
@@ -1489,7 +1498,7 @@
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J14" s="38" t="inlineStr">
@@ -1525,7 +1534,7 @@
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -1728,7 +1737,7 @@
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
@@ -1761,7 +1770,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
       <c r="G22" s="11" t="n"/>
@@ -1846,7 +1855,7 @@
       </c>
       <c r="D25" s="28" t="inlineStr">
         <is>
-          <t>Represents the total amount of clay sized particles (&lt;2 microns) in a test samples, expressed as a percentage by weight, to the total sample</t>
+          <t>Represents the total amount of clay sized particles (&lt;2 microns) in a test samples, expressed as a percentage by mass, to the total sample</t>
         </is>
       </c>
       <c r="E25" s="33" t="inlineStr">
@@ -1856,7 +1865,7 @@
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="G25" s="11" t="n"/>
@@ -1884,7 +1893,7 @@
       </c>
       <c r="D26" s="28" t="inlineStr">
         <is>
-          <t>Represents the total amount of clay sized particles (&lt;5 microns) in a test samples, expressed as a percentage by weight, to the total sample</t>
+          <t>Represents the total amount of clay sized particles (&lt;5 microns) in a test samples, expressed as a percentage by mass, to the total sample</t>
         </is>
       </c>
       <c r="E26" s="33" t="inlineStr">
@@ -1894,7 +1903,7 @@
       </c>
       <c r="F26" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="G26" s="11" t="n"/>
@@ -2267,7 +2276,7 @@
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> represents the total amount of &lt;1 micron size particles in a test sample, as a percentage of the total sample weight</t>
+          <t xml:space="preserve"> represents the total amount of &lt;1 micron size particles in a test sample, as a percentage of the total sample mass</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
@@ -2277,7 +2286,7 @@
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J38" s="38" t="inlineStr">
@@ -2644,6 +2653,11 @@
           <t>double</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>volume per volume</t>
+        </is>
+      </c>
       <c r="J50" s="38" t="inlineStr">
         <is>
           <t>x</t>
@@ -2768,7 +2782,11 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F54" s="11" t="n"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
       <c r="J54" s="38" t="inlineStr">
         <is>
           <t>x</t>
@@ -4495,7 +4513,7 @@
       </c>
       <c r="D112" s="28" t="inlineStr">
         <is>
-          <t>The percentage by weight of particles larger  than 3 inches (75 mm) and smaller than 12 inches (300 mm)</t>
+          <t>The percentage by mass of particles larger  than 3 inches (75 mm) and smaller than 12 inches (300 mm)</t>
         </is>
       </c>
       <c r="E112" s="35" t="inlineStr">
@@ -4505,7 +4523,7 @@
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J112" s="38" t="inlineStr">
@@ -4541,7 +4559,7 @@
       </c>
       <c r="F113" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J113" s="38" t="inlineStr">
@@ -4577,7 +4595,7 @@
       </c>
       <c r="F114" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J114" s="38" t="inlineStr">
@@ -4613,7 +4631,7 @@
       </c>
       <c r="F115" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J115" s="38" t="inlineStr">
@@ -4649,7 +4667,7 @@
       </c>
       <c r="F116" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J116" s="38" t="inlineStr">
@@ -4806,7 +4824,11 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F121" s="35" t="n"/>
+      <c r="F121" s="35" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="51" customHeight="1">
       <c r="A122" s="38">
@@ -5229,6 +5251,11 @@
           <t>double</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>volume per volume</t>
+        </is>
+      </c>
       <c r="J135" s="38" t="inlineStr">
         <is>
           <t>x</t>
@@ -6535,7 +6562,7 @@
       </c>
       <c r="F178" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J178" s="38" t="inlineStr">
@@ -6571,7 +6598,7 @@
       </c>
       <c r="F179" s="28" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
       <c r="J179" s="38" t="inlineStr">
@@ -6917,7 +6944,7 @@
       </c>
       <c r="F190" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7037,7 @@
       </c>
       <c r="F193" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7068,7 @@
       </c>
       <c r="F194" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7072,7 +7099,7 @@
       </c>
       <c r="F195" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7130,7 @@
       </c>
       <c r="F196" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7161,7 @@
       </c>
       <c r="F197" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7192,7 @@
       </c>
       <c r="F198" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7196,7 +7223,7 @@
       </c>
       <c r="F199" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7254,7 @@
       </c>
       <c r="F200" s="38" t="inlineStr">
         <is>
-          <t>force per force</t>
+          <t>mass per mass</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7688,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
     </row>
@@ -7692,7 +7719,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7750,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7781,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7812,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>dimensionless</t>
+          <t>pressure per pressure</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1268,11 +1268,6 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>mass per mass</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="51" customHeight="1">
       <c r="A8" s="38">
@@ -1434,11 +1429,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>mass per mass</t>
-        </is>
-      </c>
+      <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
     </row>
@@ -2653,11 +2644,6 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>volume per volume</t>
-        </is>
-      </c>
       <c r="J50" s="38" t="inlineStr">
         <is>
           <t>x</t>
@@ -2782,11 +2768,7 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>pressure</t>
-        </is>
-      </c>
+      <c r="F54" s="11" t="n"/>
       <c r="J54" s="38" t="inlineStr">
         <is>
           <t>x</t>
@@ -4824,11 +4806,7 @@
           <t>double</t>
         </is>
       </c>
-      <c r="F121" s="35" t="inlineStr">
-        <is>
-          <t>pressure</t>
-        </is>
-      </c>
+      <c r="F121" s="35" t="n"/>
     </row>
     <row r="122" ht="51" customHeight="1">
       <c r="A122" s="38">
@@ -5249,11 +5227,6 @@
       <c r="E135" s="15" t="inlineStr">
         <is>
           <t>double</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>volume per volume</t>
         </is>
       </c>
       <c r="J135" s="38" t="inlineStr">

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -8253,7 +8253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D366"/>
+  <dimension ref="A1:D371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15874,6 +15874,66 @@
       <c r="D366" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabChemicalTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>bulk_density</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>cohesion_peak</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>friction_angle_peak</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>modulus_youngs</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>poisson_ratio</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J234"/>
+  <dimension ref="A1:J237"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8238,6 +8238,87 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>bulk_unit_weight</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Unit Weight, Bulk (Natural)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Total weight (of solids and water) divided by total volume of material, representing natural conditions. Parallels bulk_density, but reported strictly as a force per volume (unit weight) rather than interchangeably as mass per volume.</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>force per volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>dry_unit_weight</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Unit Weight, Dry</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Weight of solids divided by total volume. Parallels dry_density, but reported strictly as a force per volume (unit weight) rather than interchangeably as mass per volume.</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>force per volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>unit_weight_max</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Maximum Unit Weight</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> This is a result of a compaction test. It is defined as the maximum dry unit weight that is measured when a specific type and amount of energy is used for the compaction test. This is also the value of the compacted dry unit weight when the soil is at the optimum moisture content. Parallels dry_density_max, but reported strictly as a force per volume (unit weight) rather than interchangeably as mass per volume.</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>force per volume</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8253,7 +8334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D371"/>
+  <dimension ref="A1:D378"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15934,6 +16015,120 @@
       <c r="C371" t="inlineStr">
         <is>
           <t>//diggs:parameterName</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>bulk_unit_weight</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:InsituCBRTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>bulk_unit_weight</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:InsituDensityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>bulk_unit_weight</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabCBRTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>bulk_unit_weight</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabDensityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>bulk_unit_weight</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>dry_unit_weight</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabDensityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>unit_weight_max</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabCompactionTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -8334,7 +8334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D378"/>
+  <dimension ref="A1:D608"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -15969,6 +15969,11 @@
           <t>//diggs:parameterName</t>
         </is>
       </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="B368" t="inlineStr">
@@ -15981,6 +15986,11 @@
           <t>//diggs:parameterName</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="B369" t="inlineStr">
@@ -15993,6 +16003,11 @@
           <t>//diggs:parameterName</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="B370" t="inlineStr">
@@ -16005,6 +16020,11 @@
           <t>//diggs:parameterName</t>
         </is>
       </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="B371" t="inlineStr">
@@ -16017,6 +16037,11 @@
           <t>//diggs:parameterName</t>
         </is>
       </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="B372" t="inlineStr">
@@ -16097,6 +16122,11 @@
           <t>//diggs:parameterName</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="B377" t="inlineStr">
@@ -16129,6 +16159,3916 @@
       <c r="D378" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LabCompactionTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>a_pressure</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>aashto_group_index</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>aashto_symbol</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>aggregate_abrasion_value</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>aggregate_crushing_value</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>aggregate_elongation_index</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>aggregate_flakiness_index</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>aggregate_impact_value</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>aggregate_LA_abrasion_loss</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>aggregate_la_coefficient</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>aggregate_la_wear_ratio</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>aggregate_polished_stone_value</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>aggregate_soundness_value</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>aggregate_water_absorption</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>b_pressure</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>bleed</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>blow_count</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>c_pressure</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>cbr_0.1</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>cbr_0.2</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>chalk_crushing_value</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>chloride_content</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>clay_percent_2_micron</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>clay_percent_5_micron</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>coef_consolidation_horiz</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>coef_consolidation_vertical</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>coef_curvature</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>coef_earth_pressure</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>coef_permeability</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>coef_permeability_corrected</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>coef_permeability_horiz</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>coef_permeability_vert</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>coef_uniformity</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>cohesion_residual</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>colloid_percent</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>compression_index</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>compressive_strength_unconfined</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>conductivity</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>consistency_index</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>constrained_vert_modulus</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>d10</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>d15</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>d30</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>d50</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>d60</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>d85</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>degree_of_saturation</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>depth</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>dilation_angle</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>dilatometer_modulus</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>dmt_tip_bearing</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>dry_density</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>dry_density_max</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>effective_stress_vertical</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>elapsed_time</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>filtrate_volume</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>flame_ionization_measurement</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>flow_cone_time</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>flow_mass_rate</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>flow_volume_rate</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>friction_angle_cv</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>friction_angle_residual</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>friction_ratio</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>frost_heave</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>gauge_pressure</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>gel_time</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>HFFD</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>horiz_stress_index</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>inclination</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>inclination_x</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>inclination_y</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>insitu_horizontal_stress</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Is</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Is50</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>LFFD</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>limit_pressure</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>line_loss_coeff_A</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>line_loss_coeff_B</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>line_loss_coeff_C</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>line_loss_r2</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>liquid_limit</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>liquid_limit_oven_dried</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>liquidity_index</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>LOI</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>lugeon_value</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>marsh_funnel_time</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>mass</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>mass_loss</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>material_index</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>mcv</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>mean_micro_deval_dry</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>mean_micro_deval_wet</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>menard_modulus</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>modulus_shear</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>mud_balance_density</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>n_value</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>n1_60</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>n60</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>non_plastic</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>ocr</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>p_wave_velocity</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>p0_reading</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>p1_reading</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>p2_reading</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>pen_increment</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>percent_cobbles</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>percent_fines</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>percent_gravel</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>percent_sand</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>percent_silt</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>pid_result</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>plastic_limit</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>plasticity_index</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>point_load_test_index</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>pore_pressure_equil</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>pore_pressure_est</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>pore_pressure_u1</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>pore_pressure_u2</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>pore_pressure_u3</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>preconsolidation_pressure</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>pressure_filtration_coeff</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>pumping_rate</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>recompression_index</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>redox_potential</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>relative_density</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>resistivity</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>rock_porosity</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>schmidt_hardness_value</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>sensitivity</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>set_time</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>shear_strength_drained</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>shear_strength_undrained</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>shear_strength_undrained_residual</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>shear_velocity</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>shore_hardness_value</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>shrinkage</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>shrinkage_limit</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>shrinkage_ratio</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>slake_durability_index</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>sleeve_friction</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>slump</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>soil_moisture_content</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>soil_suction</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>soil_type</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>specific_gravity_apparent</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>specific_gravity_bulk</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>specific_gravity_solids</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>sulfate_content</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>syneresis</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>syneresis_surface_area_normalized</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>t50</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>ten_percent_fines_value</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>tensile_strength</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>thrust</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>tip_resistance</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>tip_resistance_corrected</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>torque</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>transducer_pressure</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>u50</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>uscs_group_name</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>uscs_symbol</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>uscs_symbol_425</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>vertical_stress_total</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>volume_loss</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>volumetric_shrinkage</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>washout_result</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>water_content_natural</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>water_content_optimum</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>water_depth</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>water_elev</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>easily_oxidized_carbon</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>total_carbon</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>easily_oxidized_matter</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>total_organic_matter</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>free_swell_value</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>swell_pressure</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>d_value</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>c_value</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>water_content_difference</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>d84</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>d90</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>percent_coarse_gravel</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>percent_fine_gravel</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>percent_coarse_sand</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>percent_medium_sand</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>percent_fine_sand</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>aashto_percent_gravel</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>aashto_percent_coarse_sand</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>aashto_percent_fine_sand</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>differential_settlement</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>settlement_reduction_ratio</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>pore_pressure</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>reinforcement_load_fraction</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>critical_creep_load</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>modulus_of_subgrade_reaction</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>deformation_modulus_first_load</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>deformation_modulus_second_load</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>defect_depth</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>effective_radius</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>lateral_deflection</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>magnesium_content</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>cbr</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>cbr_at_95_pct_mdd</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>cbr_at_90_pct_mdd</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>cbr_at_98_100_pct_mdd</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>cbr_as_compacted</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>apparent_resistivity_min</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>apparent_resistivity_max</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>corrosivity_classification_palmer</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>thermal_conductivity</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>thermal_resistivity</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>sulfate_water_soluble</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>sulfate_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>chloride_water_soluble</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>chloride_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>magnesium_water_soluble</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>total_organic_carbon</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>carbonate_content</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>total_sulfur</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>total_sulfide</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>sulfide_acid_soluble</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>total_dissolved_solids</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>dry_unit_weight</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>unit_weight_max</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -7279,7 +7279,7 @@
       </c>
       <c r="D202" s="38" t="inlineStr">
         <is>
-          <t>The difference in settlement between two points, measured. The separation the difference is taken over is not part of this value: where a criterion expresses the limit as a gradient or angular distortion, the criterion's own basis and baseLength carry it, exactly as they do for the predicted form on diggs:RITreatedAreaDesignType.</t>
+          <t>The difference in settlement between two points, measured. The separation the difference is taken over is not part of this value: where a criterion expresses the limit as a gradient or angular distortion, the criterion's own basis and baseLength carry it, exactly as they do for the predicted form on diggs:DesignRITreatedAreaType.</t>
         </is>
       </c>
       <c r="E202" s="38" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="D203" s="38" t="inlineStr">
         <is>
-          <t>Measured settlement of the treated ground divided by the settlement of the equivalent untreated ground. The measured counterpart of diggs:RITreatedAreaDesignType/settlementEfficacy; which definition of the ratio is in use is stated by that design element's settlementEfficacyDefinition, since a measured value is only comparable against the prediction under the same definition.</t>
+          <t>Measured settlement of the treated ground divided by the settlement of the equivalent untreated ground. The measured counterpart of diggs:DesignRITreatedAreaType/settlementEfficacy; which definition of the ratio is in use is stated by that design element's settlementEfficacyDefinition, since a measured value is only comparable against the prediction under the same definition.</t>
         </is>
       </c>
       <c r="E203" s="38" t="inlineStr">

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -15009,7 +15009,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>//diggs:propertyClass</t>
+          <t>//diggs:parameterName</t>
         </is>
       </c>
       <c r="D318" s="21" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>//diggs:propertyClass</t>
+          <t>//diggs:parameterName</t>
         </is>
       </c>
       <c r="D320" s="21" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>//diggs:propertyClass</t>
+          <t>//diggs:parameterName</t>
         </is>
       </c>
       <c r="D322" s="21" t="inlineStr">
@@ -15135,7 +15135,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>//diggs:propertyClass</t>
+          <t>//diggs:parameterName</t>
         </is>
       </c>
       <c r="D324" s="21" t="inlineStr">

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8319,6 +8319,117 @@
         </is>
       </c>
     </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>maximum_axial_load</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Maximum axial load</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>The maximum compressive force carried by a specimen during an unconfined compressive strength test - the force from which the compressive strength is calculated, as that force divided by the cross-sectional area of the specimen.</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://diggsml.org/def/registry/DIGGS/0/specifications.xml#astm_c39</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>deformation_modulus_e50</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Deformation modulus E50</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>The secant modulus of a specimen at half its unconfined compressive strength: E50 is half the unconfined compressive strength divided by the axial strain at which the compressive stress reaches that half value. Where the start of the stress-strain curve has an inflection from specimen seating, the strain origin is corrected before E50 is taken.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://diggsml.org/def/registry/DIGGS/0/specifications.xml#jis_a_1216</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>length_diameter_correction_factor</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Length-to-diameter correction factor</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>The factor by which the measured compressive strength of a cylindrical specimen is multiplied where its length-to-diameter ratio is 1.75 or less, interpolated between tabulated ratios. The 2009 edition of ASTM C39 gives 0.98 at a ratio of 1.75, 0.96 at 1.50, 0.93 at 1.25 and 0.87 at 1.00.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://diggsml.org/def/registry/DIGGS/0/specifications.xml#astm_c39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8334,7 +8445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D608"/>
+  <dimension ref="A1:D611"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20069,6 +20180,57 @@
       <c r="D608" t="inlineStr">
         <is>
           <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>maximum_axial_load</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:UnconfinedCompressiveStrengthTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>deformation_modulus_e50</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:UnconfinedCompressiveStrengthTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>length_diameter_correction_factor</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:UnconfinedCompressiveStrengthTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="10020" yWindow="2560" windowWidth="35840" windowHeight="20700" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="AssociatedElements"/>
     </sheetNames>
@@ -8445,7 +8445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D611"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20231,6 +20231,23 @@
       <c r="D611" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:UnconfinedCompressiveStrengthTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>modulus_youngs</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:PerformanceCriterion</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -8445,7 +8445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D613"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20248,6 +20248,23 @@
       <c r="D612" t="inlineStr">
         <is>
           <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>relative_density</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:DesignConformanceCriterion</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -9,10 +9,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DictionaryName" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definitions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AssociatedElements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ValueBindings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
   </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -8445,7 +8446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D613"/>
+  <dimension ref="A1:D615"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20268,6 +20269,40 @@
         </is>
       </c>
     </row>
+    <row r="614">
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>compressive_strength_unconfined</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>slump</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -20278,6 +20313,135 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SubjectElement</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>RealizedValueXpath</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ReferenceValueXpath</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ReferenceSource</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ReferenceEvaluation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NormalizeByXpath</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>compressive_strength_unconfined</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>for $r in $evidence/descendant-or-self::*[diggs:results//diggs:propertyClass/@codeSpace[ends-with(., '#compressive_strength_unconfined')]] return diggs:series($r, 'compressive_strength_unconfined') ! ?2</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>slump</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>for $r in $evidence/descendant-or-self::*[diggs:results//diggs:propertyClass/@codeSpace[ends-with(., '#slump')]] return diggs:series($r, 'slump') ! ?2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>modulus_youngs</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>for $r in $evidence/descendant-or-self::*[diggs:results//diggs:propertyClass/@codeSpace[ends-with(., '#modulus_youngs')]] return diggs:series($r, 'modulus_youngs') ! ?2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>for $r in $evidence/descendant-or-self::*[diggs:results//diggs:propertyClass/@codeSpace[ends-with(., '#settlement')]] return diggs:series($r, 'settlement') ! ?2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J240"/>
+  <dimension ref="A1:J244"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8431,6 +8431,109 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>gage_reading</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Gage Reading</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Reading of a displacement gage (dial gage or displacement transducer) at one gage point, expressed as a displacement. Where several gages are read together, each is a separate property distinguished by its propertyName (for example "Dial Gage 1"); their average is reported the same way.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>applied_stress</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Applied Stress</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Normal stress applied to the ground or element through the bearing area of a load test (a plate or loaded footprint) at the time of the reading.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>jack_pressure</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Jack Pressure</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Hydraulic pressure read at the gauge of the jack applying a test load. Converted to load or stress through the jack calibration.</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>loading_phase</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Loading Phase</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Whether a load test reading or increment belongs to loading, unloading or reloading. Values from loadTestIncrementPhase.xml.</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8446,7 +8549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D615"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20300,6 +20403,210 @@
       <c r="D615" t="inlineStr">
         <is>
           <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>gage_reading</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:incrementTimeSeries</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>gage_reading</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>applied_stress</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:incrementTimeSeries</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>applied_stress</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:PlateLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>applied_stress</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ZoneLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>applied_stress</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>jack_pressure</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:incrementTimeSeries</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>jack_pressure</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>loading_phase</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:PlateLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>loading_phase</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:ZoneLoadTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>loading_phase</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:incrementTimeSeries</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:J245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8534,6 +8534,33 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>equipment_mass</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Equipment Mass</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Mass of an item of test equipment as weighed, for example a bearing plate or a jack resting on the tested element.</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>mass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8549,7 +8576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D627"/>
+  <dimension ref="A1:D629"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20607,6 +20634,40 @@
       <c r="D627" t="inlineStr">
         <is>
           <t>ancestor::diggs:incrementTimeSeries</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>equipment_mass</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:otherEquipmentProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>equipment_mass</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:K245"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -1108,6 +1108,11 @@
           <t>SLD Changed</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ValueCodeSpace</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="68" customHeight="1">
       <c r="A2" s="38">
@@ -8525,12 +8530,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Whether a load test reading or increment belongs to loading, unloading or reloading. Values from loadTestIncrementPhase.xml.</t>
+          <t>Whether a load test reading or increment belongs to seating, loading, unloading or reloading.</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>https://diggsml.org/def/codes/DIGGS/0.1/loadTestIncrementPhase.xml</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K245"/>
+  <dimension ref="A1:K258"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8571,6 +8571,312 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>calibration_reference_value</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Calibration Reference Value</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Value of the reference standard applied to the item at one calibration point, in the unit of the quantity calibrated (for example bar for a pressure gauge).</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>calibration_indicated_value</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Calibration Indicated Value</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Value the item under calibration indicated at one calibration point, in the unit of the quantity calibrated.</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>calibration_deviation</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Calibration Deviation</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Difference between the value the item indicated and the reference value applied, at one calibration point, as reported on the certificate.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>calibration_expanded_uncertainty</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Calibration Expanded Uncertainty</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Expanded uncertainty of the calibration at one point, at the coverage factor stated for the calibration (coverage_factor).</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>instrument_resolution</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Instrument Resolution</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Smallest change in the quantity measured that the instrument displays, as stated on the calibration certificate.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>maximum_expanded_uncertainty</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Maximum Expanded Uncertainty</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Largest expanded uncertainty over the calibrated range, as stated on the calibration certificate, in the unit of the quantity calibrated.</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>coverage_factor</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Coverage Factor</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Factor multiplying the standard uncertainty to give the expanded uncertainty reported; k = 2 corresponds to a coverage probability of approximately 95 %.</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>calibrated_range_minimum</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Calibrated Range Minimum</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Lower limit of the range over which the instrument was calibrated, in the unit of the quantity calibrated.</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>calibrated_range_maximum</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Calibrated Range Maximum</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Upper limit of the range over which the instrument was calibrated, in the unit of the quantity calibrated.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>acceptance_tolerance</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Acceptance Tolerance</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>The tolerance the instrument is accepted to, as stated on the calibration certificate - a limit or a reference to the manufacturer's specification.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>jack_ram_area</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Jack Ram Area</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Area of the hydraulic jack ram, as stated on the calibration certificate, used to convert jack pressure to force.</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>ambient_temperature</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ambient Temperature</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Air temperature in the laboratory or on site while a calibration was performed. State the permitted variation as the minimum and maximum value.</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>thermodynamic temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>relative_humidity</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Relative Humidity</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Relative humidity of the air while a calibration was performed. State the permitted variation as the minimum and maximum value.</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8586,7 +8892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D629"/>
+  <dimension ref="A1:D655"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -20676,6 +20982,448 @@
         </is>
       </c>
       <c r="D629" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>calibration_reference_value</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationResults</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>calibration_reference_value</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>calibration_indicated_value</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationResults</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>calibration_indicated_value</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>calibration_deviation</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationResults</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>calibration_deviation</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>calibration_expanded_uncertainty</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationResults</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>calibration_expanded_uncertainty</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>instrument_resolution</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>instrument_resolution</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>maximum_expanded_uncertainty</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>maximum_expanded_uncertainty</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>coverage_factor</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>coverage_factor</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>calibrated_range_minimum</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>calibrated_range_minimum</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>calibrated_range_maximum</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>calibrated_range_maximum</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>acceptance_tolerance</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>acceptance_tolerance</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>jack_ram_area</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationValues</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>jack_ram_area</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>ambient_temperature</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationConditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>ambient_temperature</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>relative_humidity</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:calibrationConditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>relative_humidity</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
         <is>
           <t>ancestor::diggs:characteristicProperty</t>
         </is>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -21444,7 +21444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21551,12 +21551,34 @@
           <t>settlement</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>diggs:LoadTransferPlatform</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>value_at</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>let $r := $evidence/diggs:outcome/*[1], $x := diggs:series($r, 'applied_stress'), $y := diggs:series($r, 'settlement'), $p := diggs:series($r, 'loading_phase') return for $i in 1 to count($y) return if ($p[$i]?2 = 'loading') then [$x[$i]?2, $y[$i]?2] else ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>direct</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>for $r in $evidence/descendant-or-self::*[diggs:results//diggs:propertyClass/@codeSpace[ends-with(., '#settlement')]] return diggs:series($r, 'settlement') ! ?2</t>
         </is>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K258"/>
+  <dimension ref="A1:K261"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8877,6 +8877,87 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>toe_depth</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Toe Depth</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>The depth from the pile or element head to the toe reflection of a low-strain integrity test record, taken at the largest-amplitude reflection of the record and calculated from its travel time and the assumed wave speed. A result of diggs:LowStrainIntegrityTest. Compare with the as-built length of the element through toe_depth_deviation; defect_depth is the depth of a reflection above the toe.</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>toe_depth_deviation</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Toe Depth Deviation</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>The difference between the toe depth of a low-strain integrity test and the as-built length of the element, without sign, as a percentage of the as-built length. The assumed wave speed alone can move a reflected depth by about ten percent, which sets the order of a limit on this property.</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>relative_reflection_amplitude</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Relative Reflection Amplitude</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>The height of a reflection in a low-strain integrity test record relative to the height of the initial impact peak, both read from the same record. A reflection of the same sign as the impact, above the toe, indicates a reduction in impedance - a neck, a crack or poor concrete - and its relative height approximates the reflection coefficient where the amplification of the record balances the toe reflection against the impact. Stated for the largest such reflection above the toe.</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8892,7 +8973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D655"/>
+  <dimension ref="A1:D663"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -21424,6 +21505,142 @@
         </is>
       </c>
       <c r="D655" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>toe_depth</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>toe_depth_deviation</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>relative_reflection_amplitude</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>toe_depth_deviation</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>relative_reflection_amplitude</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:PerformanceCriterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>toe_depth</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>toe_depth_deviation</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>relative_reflection_amplitude</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
         <is>
           <t>ancestor::diggs:characteristicProperty</t>
         </is>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K261"/>
+  <dimension ref="A1:K270"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -8958,6 +8958,249 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>normalized_velocity</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Normalized Velocity</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>The velocity of the head of a pile or element in a low-strain integrity test record as evaluated: averaged over the impacts, amplified as the procedure states and normalized so that the impact peak has a fixed height. A number without a unit, comparable only with the impact of the same record. A column of the depth-indexed result of diggs:LowStrainIntegrityTest.</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>normalized_force</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Normalized Force</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>The force applied to the head of a pile or element in a low-strain integrity test with an instrumented hammer, normalized to the same scale as the normalized velocity of the record. A number without a unit. A column of the result of diggs:LowStrainIntegrityTest.</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>impact_force</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Impact Force</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>The force applied to the head of a pile or element by the hammer of a low-strain integrity test, measured by an instrumented hammer. A column of the result of diggs:LowStrainIntegrityTest.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>relative_impedance</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Relative Impedance</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>The impedance of a pile or element at a depth relative to its impedance at the head, as reconstructed from a low-strain integrity test record; 1 where the section and the concrete equal those at the head. A column of the depth-indexed result of diggs:LowStrainIntegrityTest.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>A frequency at which a frequency-domain record is stated - for example a row of the mobility record of a transient response low-strain integrity test (diggs:LowStrainIntegrityTest/frequencyResponse).</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>mobility</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Mobility</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>The ratio of the velocity transform to the force transform at the head of a pile or element at a frequency, in a transient response low-strain integrity test: velocity per force (s/kg, equal to m/(N.s)). A column of diggs:LowStrainIntegrityTest/frequencyResponse. Not the fluid mobility of a porous medium.</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>time per mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>characteristic_mobility</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Characteristic Mobility</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>The mean mobility over the range of resonant frequencies of a transient response low-strain integrity test record. For a uniform element it approximates the reciprocal of the product of concrete density, wave speed and cross-sectional area, so it reflects the section and the quality of the concrete.</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>time per mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>dynamic_stiffness</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Dynamic Stiffness</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>The ratio of force to displacement at the head of a pile or element at low frequency, read from the initial slope of the mobility record of a transient response low-strain integrity test. It reflects the element and the soil around it.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>force per length</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>mobility_ratio</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Mobility Ratio</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>The ratio of the peak mobility to the characteristic mobility of a transient response low-strain integrity test record. A number without a unit.</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -8973,7 +9216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D663"/>
+  <dimension ref="A1:D682"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -21643,6 +21886,329 @@
       <c r="D663" t="inlineStr">
         <is>
           <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>normalized_velocity</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>normalized_force</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>impact_force</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>relative_impedance</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>mobility</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>characteristic_mobility</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>dynamic_stiffness</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>mobility_ratio</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>characteristic_mobility</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>characteristic_mobility</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>dynamic_stiffness</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>dynamic_stiffness</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>mobility_ratio</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>mobility_ratio</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:characteristicProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>elapsed_time</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>toe_depth</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>defect_depth</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>relative_reflection_amplitude</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -8890,7 +8890,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>The depth from the pile or element head to the toe reflection of a low-strain integrity test record, taken at the largest-amplitude reflection of the record and calculated from its travel time and the assumed wave speed. A result of diggs:LowStrainIntegrityTest. Compare with the as-built length of the element through toe_depth_deviation; defect_depth is the depth of a reflection above the toe.</t>
+          <t>The depth from the pile or element head to the toe reflection of a low-strain integrity test record: the deepest reflection of the record, found by working up from the bottom of the record, taken at its first amplitude maximum (or at its starting deflection where the start pulse of the record is referenced to its starting deflection). Reading from the bottom separates the toe from internal defects, which lie above it. The depth is calculated from the travel time and the assumed wave speed. A result of diggs:LowStrainIntegrityTest. Compare with the length of the element through toe_depth_deviation; defect_depth is the depth of a reflection above the toe.</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -1042,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K270"/>
+  <dimension ref="A1:K271"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="38" min="1" max="1"/>
@@ -9201,6 +9201,38 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>relative_toe_amplitude</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Relative Toe Amplitude</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>The height of the toe reflection of a low-strain integrity test record relative to the height of the initial impact peak, both read from the same record: 1 where the amplification balances the toe reflection against the impact, above 1 where the record is amplified past that balance and below 1 where it is not amplified up to it. A result of diggs:LowStrainIntegrityTest. See relative_reflection_amplitude.</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -9216,7 +9248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D682"/>
+  <dimension ref="A1:D684"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -22207,6 +22239,40 @@
         </is>
       </c>
       <c r="D682" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>relative_toe_amplitude</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>//diggs:propertyClass</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>relative_toe_amplitude</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
         <is>
           <t>ancestor::diggs:measurement//diggs:procedure/diggs:LowStrainIntegrityTest</t>
         </is>
@@ -22227,7 +22293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22364,6 +22430,72 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>for $r in $evidence/descendant-or-self::*[diggs:results//diggs:propertyClass/@codeSpace[ends-with(., '#settlement')]] return diggs:series($r, 'settlement') ! ?2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>toe_depth_deviation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>diggs:Test</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>let $t := diggs:otherMeasurementProperty/diggs:AuthorizedParameter[diggs:parameterName/@codeSpace[ends-with(., '#toe_depth')]]/diggs:parameterValue, $l := diggs:procedure/*/diggs:referenceLength return if (exists($t) and exists($l)) then abs(number($t) - number($l)) * 100 div number($l) else ()</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>relative_reflection_amplitude</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>diggs:Test</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>diggs:otherMeasurementProperty/diggs:AuthorizedParameter[diggs:parameterName/@codeSpace[ends-with(., '#relative_reflection_amplitude')]]/diggs:parameterValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>relative_toe_amplitude</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>diggs:Test</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>diggs:otherMeasurementProperty/diggs:AuthorizedParameter[diggs:parameterName/@codeSpace[ends-with(., '#relative_toe_amplitude')]]/diggs:parameterValue</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/properties.xlsx
@@ -22407,7 +22407,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>value_at</t>
+          <t>value at</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
